--- a/INFORME/evidencias.xlsx
+++ b/INFORME/evidencias.xlsx
@@ -9,15 +9,17 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19170" windowHeight="5175" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19170" windowHeight="5175" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="botones y volante prueba 1 y 2 " sheetId="1" r:id="rId1"/>
     <sheet name="prueba 3 y 4 atencia fps" sheetId="2" r:id="rId2"/>
     <sheet name="prueba 3 bloque 2" sheetId="3" r:id="rId3"/>
     <sheet name="analisis de costos" sheetId="4" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="126">
   <si>
     <t>total</t>
   </si>
@@ -400,13 +402,19 @@
   <si>
     <t>30437 Bs.</t>
   </si>
+  <si>
+    <t>resumen porsentaje de errores</t>
+  </si>
+  <si>
+    <t>Nombre de prueba</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -1036,7 +1044,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1051,15 +1059,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1082,16 +1081,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1108,15 +1098,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
@@ -1125,10 +1106,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1173,15 +1154,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1263,15 +1235,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1328,6 +1291,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1343,6 +1353,4410 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Prueba de los 100 tiros</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.17116007128673918"/>
+          <c:y val="0.15521692925849973"/>
+          <c:w val="0.7533452823891521"/>
+          <c:h val="0.70959135316418775"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:softEdge rad="0"/>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.8452213880421799E-2"/>
+                  <c:y val="0"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-BA22-4C32-B123-B759F24AA6F6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.665768744040618E-2"/>
+                  <c:y val="-8.4919489796548163E-17"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-BA22-4C32-B123-B759F24AA6F6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.665768744040618E-2"/>
+                  <c:y val="-8.4919489796548163E-17"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-BA22-4C32-B123-B759F24AA6F6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="4.665768744040618E-2"/>
+                  <c:y val="0"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-BA22-4C32-B123-B759F24AA6F6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$6:$B$13</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Boton 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Boton 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Boton 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Boton 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Boton lim</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Boton su</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>encoder inc.</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>encoder ext.</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$C$6:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.02</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BA22-4C32-B123-B759F24AA6F6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="732809551"/>
+        <c:axId val="732806223"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="732809551"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732806223"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="l"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="732806223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="732809551"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:softEdge rad="0"/>
+        </a:effectLst>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:solidFill>
+        <a:schemeClr val="accent1"/>
+      </a:solidFill>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Prueba de volantes &lt;10° por deteccion, con giros de 360</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$20:$B$23</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>volante 1 izq.</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>volante 1 der.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>volante 2 izq.</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>volante 2 der.</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$C$20:$C$23</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.18107416879795402</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17025901942645572</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.9062316037340459E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9813664596272993E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2DCF-499F-B4D0-4C9FCAD994D4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="115"/>
+        <c:overlap val="-20"/>
+        <c:axId val="883743743"/>
+        <c:axId val="883740831"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="883743743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="883740831"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="883740831"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="883743743"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Avance del endoscopio por centimetros</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$C$51:$C$60</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>9.9999999999999638E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4778325123152743E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0000000000000071E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.6666666666666666E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9607843137254902E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.333333333333324E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.7142857142857958E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.0000000000000072E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.2727272727272728E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.5151515151515152E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7F49-4ECD-BC38-0C0B0ABE7532}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="84"/>
+        <c:axId val="832042095"/>
+        <c:axId val="832042927"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout/>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-7F49-4ECD-BC38-0C0B0ABE7532}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$D$51:$D$60</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3.5797924185348121E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.5797924185348121E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5797924185348121E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.5797924185348121E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.5797924185348121E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.5797924185348121E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.5797924185348121E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.5797924185348121E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.5797924185348121E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.5797924185348121E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7F49-4ECD-BC38-0C0B0ABE7532}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="841389615"/>
+        <c:axId val="727178575"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="832042095"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="832042927"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="832042927"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="832042095"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="727178575"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="841389615"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="841389615"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="727178575"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Avance del endoscopio por centimetros</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$C$65:$C$74</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>8.0000000000000071E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.0000000000000038E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0000000000000071E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.6666666666666666E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.6666666666666666E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.5714285714285715E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.0000000000000038E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.5454545454545456E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.0606060606061465E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-43B6-44CE-B5AE-D22EEBD294CF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="84"/>
+        <c:axId val="832042095"/>
+        <c:axId val="832042927"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:layout/>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-43B6-44CE-B5AE-D22EEBD294CF}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$D$65:$D$74</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>6.9056277056277079E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.9056277056277079E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.9056277056277079E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.9056277056277079E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.9056277056277079E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.9056277056277079E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.9056277056277079E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.9056277056277079E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.9056277056277079E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.9056277056277079E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-43B6-44CE-B5AE-D22EEBD294CF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="832042095"/>
+        <c:axId val="832042927"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="832042095"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="832042927"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="832042927"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="832042095"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="304">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="222">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="328">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="95000"/>
+              <a:lumOff val="5000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+      </a:gradFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="328">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="95000"/>
+              <a:lumOff val="5000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+      </a:gradFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>568484</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>141861</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>369794</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18036</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>566737</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>566737</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>261937</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>271461</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>390524</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Gráfico 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1629,82 +6043,82 @@
   <sheetData>
     <row r="2" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M3" s="21" t="s">
+      <c r="M3" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="10"/>
+      <c r="N3" s="111"/>
+      <c r="O3" s="111"/>
+      <c r="P3" s="111"/>
+      <c r="Q3" s="113"/>
     </row>
     <row r="4" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="10"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="21" t="s">
+      <c r="B4" s="112" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="113"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="110" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="10"/>
-      <c r="P4" s="23" t="s">
+      <c r="O4" s="113"/>
+      <c r="P4" s="114" t="s">
         <v>30</v>
       </c>
-      <c r="Q4" s="24"/>
+      <c r="Q4" s="115"/>
     </row>
     <row r="5" spans="2:28" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="29" t="s">
+      <c r="M5" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="N5" s="30" t="s">
+      <c r="N5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="50" t="s">
+      <c r="O5" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="P5" s="31" t="s">
+      <c r="P5" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="Q5" s="50" t="s">
+      <c r="Q5" s="41" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B6" s="14">
+      <c r="B6" s="11">
         <v>1</v>
       </c>
       <c r="C6" s="3">
@@ -1728,29 +6142,29 @@
       <c r="I6" s="3">
         <v>1</v>
       </c>
-      <c r="J6" s="15">
-        <v>1</v>
-      </c>
-      <c r="M6" s="25">
-        <v>1</v>
-      </c>
-      <c r="N6" s="26">
+      <c r="J6" s="12">
+        <v>1</v>
+      </c>
+      <c r="M6" s="19">
+        <v>1</v>
+      </c>
+      <c r="N6" s="20">
         <v>51</v>
       </c>
-      <c r="O6" s="52">
+      <c r="O6" s="43">
         <f>360/N6</f>
         <v>7.0588235294117645</v>
       </c>
-      <c r="P6" s="47">
+      <c r="P6" s="38">
         <v>48</v>
       </c>
-      <c r="Q6" s="48">
+      <c r="Q6" s="39">
         <f>360/P6</f>
         <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B7" s="14">
+      <c r="B7" s="11">
         <v>2</v>
       </c>
       <c r="C7" s="3">
@@ -1774,29 +6188,29 @@
       <c r="I7" s="3">
         <v>0</v>
       </c>
-      <c r="J7" s="15">
-        <v>1</v>
-      </c>
-      <c r="M7" s="20">
+      <c r="J7" s="12">
+        <v>1</v>
+      </c>
+      <c r="M7" s="17">
         <v>2</v>
       </c>
-      <c r="N7" s="18">
+      <c r="N7" s="15">
         <v>45</v>
       </c>
-      <c r="O7" s="52">
+      <c r="O7" s="43">
         <f t="shared" ref="O7:O15" si="0">360/N7</f>
         <v>8</v>
       </c>
-      <c r="P7" s="18">
+      <c r="P7" s="15">
         <v>46</v>
       </c>
-      <c r="Q7" s="27">
+      <c r="Q7" s="21">
         <f t="shared" ref="Q7:Q14" si="1">360/P7</f>
         <v>7.8260869565217392</v>
       </c>
     </row>
     <row r="8" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B8" s="14">
+      <c r="B8" s="11">
         <v>3</v>
       </c>
       <c r="C8" s="3">
@@ -1820,29 +6234,29 @@
       <c r="I8" s="3">
         <v>1</v>
       </c>
-      <c r="J8" s="15">
-        <v>1</v>
-      </c>
-      <c r="M8" s="20">
+      <c r="J8" s="12">
+        <v>1</v>
+      </c>
+      <c r="M8" s="17">
         <v>3</v>
       </c>
-      <c r="N8" s="18">
+      <c r="N8" s="15">
         <v>46</v>
       </c>
-      <c r="O8" s="52">
+      <c r="O8" s="43">
         <f t="shared" si="0"/>
         <v>7.8260869565217392</v>
       </c>
-      <c r="P8" s="18">
+      <c r="P8" s="15">
         <v>45</v>
       </c>
-      <c r="Q8" s="27">
+      <c r="Q8" s="21">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="14">
+      <c r="B9" s="11">
         <v>4</v>
       </c>
       <c r="C9" s="3">
@@ -1866,29 +6280,29 @@
       <c r="I9" s="3">
         <v>1</v>
       </c>
-      <c r="J9" s="15">
-        <v>1</v>
-      </c>
-      <c r="M9" s="20">
+      <c r="J9" s="12">
+        <v>1</v>
+      </c>
+      <c r="M9" s="17">
         <v>4</v>
       </c>
-      <c r="N9" s="18">
+      <c r="N9" s="15">
         <v>46</v>
       </c>
-      <c r="O9" s="52">
+      <c r="O9" s="43">
         <f t="shared" si="0"/>
         <v>7.8260869565217392</v>
       </c>
-      <c r="P9" s="18">
+      <c r="P9" s="15">
         <v>45</v>
       </c>
-      <c r="Q9" s="27">
+      <c r="Q9" s="21">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="14">
+      <c r="B10" s="11">
         <v>5</v>
       </c>
       <c r="C10" s="3">
@@ -1912,42 +6326,42 @@
       <c r="I10" s="3">
         <v>1</v>
       </c>
-      <c r="J10" s="15">
-        <v>1</v>
-      </c>
-      <c r="M10" s="20">
+      <c r="J10" s="12">
+        <v>1</v>
+      </c>
+      <c r="M10" s="17">
         <v>5</v>
       </c>
-      <c r="N10" s="18">
+      <c r="N10" s="15">
         <v>45</v>
       </c>
-      <c r="O10" s="52">
+      <c r="O10" s="43">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="P10" s="18">
+      <c r="P10" s="15">
         <v>46</v>
       </c>
-      <c r="Q10" s="27">
+      <c r="Q10" s="21">
         <f t="shared" si="1"/>
         <v>7.8260869565217392</v>
       </c>
-      <c r="T10" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="U10" s="34"/>
-      <c r="V10" s="34"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="32"/>
-      <c r="Y10" s="21" t="s">
+      <c r="T10" s="116" t="s">
+        <v>1</v>
+      </c>
+      <c r="U10" s="117"/>
+      <c r="V10" s="117"/>
+      <c r="W10" s="118"/>
+      <c r="X10" s="26"/>
+      <c r="Y10" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="Z10" s="9"/>
-      <c r="AA10" s="9"/>
-      <c r="AB10" s="10"/>
+      <c r="Z10" s="111"/>
+      <c r="AA10" s="111"/>
+      <c r="AB10" s="113"/>
     </row>
     <row r="11" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="14">
+      <c r="B11" s="11">
         <v>6</v>
       </c>
       <c r="C11" s="3">
@@ -1971,53 +6385,53 @@
       <c r="I11" s="3">
         <v>1</v>
       </c>
-      <c r="J11" s="15">
-        <v>1</v>
-      </c>
-      <c r="M11" s="20">
+      <c r="J11" s="12">
+        <v>1</v>
+      </c>
+      <c r="M11" s="17">
         <v>6</v>
       </c>
-      <c r="N11" s="18">
+      <c r="N11" s="15">
         <v>45</v>
       </c>
-      <c r="O11" s="52">
+      <c r="O11" s="43">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="P11" s="18">
+      <c r="P11" s="15">
         <v>47</v>
       </c>
-      <c r="Q11" s="27">
+      <c r="Q11" s="21">
         <f t="shared" si="1"/>
         <v>7.6595744680851068</v>
       </c>
-      <c r="T11" s="36" t="s">
+      <c r="T11" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="U11" s="37" t="s">
+      <c r="U11" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="V11" s="40" t="s">
+      <c r="V11" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="W11" s="41" t="s">
+      <c r="W11" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="Y11" s="36" t="s">
+      <c r="Y11" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="Z11" s="37" t="s">
+      <c r="Z11" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="AA11" s="37" t="s">
+      <c r="AA11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="AB11" s="38" t="s">
+      <c r="AB11" s="29" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B12" s="14">
+      <c r="B12" s="11">
         <v>7</v>
       </c>
       <c r="C12" s="3">
@@ -2041,57 +6455,57 @@
       <c r="I12" s="3">
         <v>1</v>
       </c>
-      <c r="J12" s="15">
-        <v>1</v>
-      </c>
-      <c r="M12" s="20">
+      <c r="J12" s="12">
+        <v>1</v>
+      </c>
+      <c r="M12" s="17">
         <v>7</v>
       </c>
-      <c r="N12" s="18">
+      <c r="N12" s="15">
         <v>46</v>
       </c>
-      <c r="O12" s="52">
+      <c r="O12" s="43">
         <f t="shared" si="0"/>
         <v>7.8260869565217392</v>
       </c>
-      <c r="P12" s="18">
+      <c r="P12" s="15">
         <v>45</v>
       </c>
-      <c r="Q12" s="27">
+      <c r="Q12" s="21">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="T12" s="18" t="s">
+      <c r="T12" s="15" t="s">
         <v>3</v>
       </c>
       <c r="U12" s="2">
         <v>100</v>
       </c>
-      <c r="V12" s="44">
+      <c r="V12" s="35">
         <f>C106</f>
         <v>100</v>
       </c>
-      <c r="W12" s="42">
-        <f>(U12-V12)/100</f>
+      <c r="W12" s="33">
+        <f t="shared" ref="W12:W19" si="2">(U12-V12)/100</f>
         <v>0</v>
       </c>
-      <c r="Y12" s="56" t="s">
+      <c r="Y12" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="Z12" s="12">
+      <c r="Z12" s="9">
         <v>8</v>
       </c>
-      <c r="AA12" s="57">
+      <c r="AA12" s="48">
         <f>O16</f>
         <v>7.818925831202046</v>
       </c>
-      <c r="AB12" s="58">
+      <c r="AB12" s="49">
         <f>Z12-AA12</f>
         <v>0.18107416879795402</v>
       </c>
     </row>
     <row r="13" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B13" s="14">
+      <c r="B13" s="11">
         <v>8</v>
       </c>
       <c r="C13" s="3">
@@ -2115,57 +6529,57 @@
       <c r="I13" s="3">
         <v>1</v>
       </c>
-      <c r="J13" s="15">
-        <v>1</v>
-      </c>
-      <c r="M13" s="20">
+      <c r="J13" s="12">
+        <v>1</v>
+      </c>
+      <c r="M13" s="17">
         <v>8</v>
       </c>
-      <c r="N13" s="18">
+      <c r="N13" s="15">
         <v>46</v>
       </c>
-      <c r="O13" s="52">
+      <c r="O13" s="43">
         <f t="shared" si="0"/>
         <v>7.8260869565217392</v>
       </c>
-      <c r="P13" s="18">
+      <c r="P13" s="15">
         <v>46</v>
       </c>
-      <c r="Q13" s="27">
+      <c r="Q13" s="21">
         <f t="shared" si="1"/>
         <v>7.8260869565217392</v>
       </c>
-      <c r="T13" s="18" t="s">
+      <c r="T13" s="15" t="s">
         <v>5</v>
       </c>
       <c r="U13" s="2">
         <v>100</v>
       </c>
-      <c r="V13" s="44">
+      <c r="V13" s="35">
         <f>D106</f>
         <v>100</v>
       </c>
-      <c r="W13" s="42">
-        <f>(U13-V13)/100</f>
+      <c r="W13" s="33">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Y13" s="18" t="s">
+      <c r="Y13" s="15" t="s">
         <v>27</v>
       </c>
       <c r="Z13" s="2">
         <v>8</v>
       </c>
-      <c r="AA13" s="54">
+      <c r="AA13" s="45">
         <f>Q16</f>
         <v>7.8297409805735443</v>
       </c>
-      <c r="AB13" s="59">
+      <c r="AB13" s="50">
         <f>Z13-AA13</f>
         <v>0.17025901942645572</v>
       </c>
     </row>
     <row r="14" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B14" s="14">
+      <c r="B14" s="11">
         <v>9</v>
       </c>
       <c r="C14" s="3">
@@ -2189,57 +6603,57 @@
       <c r="I14" s="3">
         <v>1</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="12">
         <v>0</v>
       </c>
-      <c r="M14" s="20">
+      <c r="M14" s="17">
         <v>9</v>
       </c>
-      <c r="N14" s="18">
+      <c r="N14" s="15">
         <v>46</v>
       </c>
-      <c r="O14" s="52">
+      <c r="O14" s="43">
         <f t="shared" si="0"/>
         <v>7.8260869565217392</v>
       </c>
-      <c r="P14" s="18">
+      <c r="P14" s="15">
         <v>45</v>
       </c>
-      <c r="Q14" s="27">
+      <c r="Q14" s="21">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="T14" s="18" t="s">
+      <c r="T14" s="15" t="s">
         <v>6</v>
       </c>
       <c r="U14" s="2">
         <v>100</v>
       </c>
-      <c r="V14" s="44">
+      <c r="V14" s="35">
         <f>E106</f>
         <v>99</v>
       </c>
-      <c r="W14" s="42">
-        <f>(U14-V14)/100</f>
+      <c r="W14" s="33">
+        <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
-      <c r="Y14" s="18" t="s">
+      <c r="Y14" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="Z14" s="55">
+      <c r="Z14" s="46">
         <v>8</v>
       </c>
-      <c r="AA14" s="54">
+      <c r="AA14" s="45">
         <f>O33</f>
         <v>7.9509376839626595</v>
       </c>
-      <c r="AB14" s="59">
+      <c r="AB14" s="50">
         <f>Z14-AA14</f>
         <v>4.9062316037340459E-2</v>
       </c>
     </row>
     <row r="15" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="14">
+      <c r="B15" s="11">
         <v>10</v>
       </c>
       <c r="C15" s="3">
@@ -2263,57 +6677,57 @@
       <c r="I15" s="3">
         <v>1</v>
       </c>
-      <c r="J15" s="15">
-        <v>1</v>
-      </c>
-      <c r="M15" s="20">
+      <c r="J15" s="12">
+        <v>1</v>
+      </c>
+      <c r="M15" s="17">
         <v>10</v>
       </c>
-      <c r="N15" s="18">
+      <c r="N15" s="15">
         <v>45</v>
       </c>
-      <c r="O15" s="52">
+      <c r="O15" s="43">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="P15" s="19">
+      <c r="P15" s="16">
         <v>47</v>
       </c>
-      <c r="Q15" s="49">
+      <c r="Q15" s="40">
         <f>360/P15</f>
         <v>7.6595744680851068</v>
       </c>
-      <c r="T15" s="18" t="s">
+      <c r="T15" s="15" t="s">
         <v>7</v>
       </c>
       <c r="U15" s="2">
         <v>100</v>
       </c>
-      <c r="V15" s="44">
+      <c r="V15" s="35">
         <f>F106</f>
         <v>100</v>
       </c>
-      <c r="W15" s="42">
-        <f t="shared" ref="W15:W19" si="2">(U15-V15)/100</f>
+      <c r="W15" s="33">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Y15" s="19" t="s">
+      <c r="Y15" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="Z15" s="60">
+      <c r="Z15" s="51">
         <v>8</v>
       </c>
-      <c r="AA15" s="61">
+      <c r="AA15" s="52">
         <f>Q33</f>
         <v>7.970186335403727</v>
       </c>
-      <c r="AB15" s="62">
+      <c r="AB15" s="53">
         <f>Z15-AA15</f>
         <v>2.9813664596272993E-2</v>
       </c>
     </row>
     <row r="16" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="14">
+      <c r="B16" s="11">
         <v>11</v>
       </c>
       <c r="C16" s="3">
@@ -2337,39 +6751,39 @@
       <c r="I16" s="3">
         <v>1</v>
       </c>
-      <c r="J16" s="15">
-        <v>1</v>
-      </c>
-      <c r="M16" s="21" t="s">
+      <c r="J16" s="12">
+        <v>1</v>
+      </c>
+      <c r="M16" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="N16" s="9"/>
-      <c r="O16" s="92">
+      <c r="N16" s="111"/>
+      <c r="O16" s="80">
         <f>SUM(O6:O15)/M15</f>
         <v>7.818925831202046</v>
       </c>
-      <c r="P16" s="93"/>
-      <c r="Q16" s="94">
+      <c r="P16" s="81"/>
+      <c r="Q16" s="82">
         <f>SUM(Q6:Q15)/M15</f>
         <v>7.8297409805735443</v>
       </c>
-      <c r="T16" s="18" t="s">
+      <c r="T16" s="15" t="s">
         <v>15</v>
       </c>
       <c r="U16" s="2">
         <v>100</v>
       </c>
-      <c r="V16" s="44">
+      <c r="V16" s="35">
         <f>G106</f>
         <v>100</v>
       </c>
-      <c r="W16" s="42">
+      <c r="W16" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B17" s="14">
+      <c r="B17" s="11">
         <v>12</v>
       </c>
       <c r="C17" s="3">
@@ -2393,27 +6807,27 @@
       <c r="I17" s="3">
         <v>1</v>
       </c>
-      <c r="J17" s="15">
-        <v>1</v>
-      </c>
-      <c r="P17" s="39"/>
-      <c r="T17" s="18" t="s">
+      <c r="J17" s="12">
+        <v>1</v>
+      </c>
+      <c r="P17" s="30"/>
+      <c r="T17" s="15" t="s">
         <v>16</v>
       </c>
       <c r="U17" s="2">
         <v>100</v>
       </c>
-      <c r="V17" s="44">
+      <c r="V17" s="35">
         <f>H106</f>
         <v>99</v>
       </c>
-      <c r="W17" s="42">
+      <c r="W17" s="33">
         <f t="shared" si="2"/>
         <v>0.01</v>
       </c>
     </row>
     <row r="18" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B18" s="14">
+      <c r="B18" s="11">
         <v>13</v>
       </c>
       <c r="C18" s="3">
@@ -2437,26 +6851,26 @@
       <c r="I18" s="3">
         <v>1</v>
       </c>
-      <c r="J18" s="15">
-        <v>1</v>
-      </c>
-      <c r="T18" s="18" t="s">
+      <c r="J18" s="12">
+        <v>1</v>
+      </c>
+      <c r="T18" s="15" t="s">
         <v>18</v>
       </c>
       <c r="U18" s="2">
         <v>100</v>
       </c>
-      <c r="V18" s="44">
+      <c r="V18" s="35">
         <f>I106</f>
         <v>98</v>
       </c>
-      <c r="W18" s="42">
+      <c r="W18" s="33">
         <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
     </row>
     <row r="19" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="14">
+      <c r="B19" s="11">
         <v>14</v>
       </c>
       <c r="C19" s="3">
@@ -2480,26 +6894,26 @@
       <c r="I19" s="3">
         <v>1</v>
       </c>
-      <c r="J19" s="15">
-        <v>1</v>
-      </c>
-      <c r="T19" s="19" t="s">
+      <c r="J19" s="12">
+        <v>1</v>
+      </c>
+      <c r="T19" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="U19" s="45">
+      <c r="U19" s="36">
         <v>100</v>
       </c>
-      <c r="V19" s="46">
+      <c r="V19" s="37">
         <f>J106</f>
         <v>98</v>
       </c>
-      <c r="W19" s="43">
+      <c r="W19" s="34">
         <f t="shared" si="2"/>
         <v>0.02</v>
       </c>
     </row>
     <row r="20" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="14">
+      <c r="B20" s="11">
         <v>15</v>
       </c>
       <c r="C20" s="3">
@@ -2523,19 +6937,19 @@
       <c r="I20" s="3">
         <v>1</v>
       </c>
-      <c r="J20" s="15">
-        <v>1</v>
-      </c>
-      <c r="M20" s="21" t="s">
+      <c r="J20" s="12">
+        <v>1</v>
+      </c>
+      <c r="M20" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="10"/>
+      <c r="N20" s="111"/>
+      <c r="O20" s="111"/>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="113"/>
     </row>
     <row r="21" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="14">
+      <c r="B21" s="11">
         <v>16</v>
       </c>
       <c r="C21" s="3">
@@ -2559,21 +6973,21 @@
       <c r="I21" s="3">
         <v>1</v>
       </c>
-      <c r="J21" s="15">
-        <v>1</v>
-      </c>
-      <c r="M21" s="22"/>
-      <c r="N21" s="21" t="s">
+      <c r="J21" s="12">
+        <v>1</v>
+      </c>
+      <c r="M21" s="18"/>
+      <c r="N21" s="110" t="s">
         <v>32</v>
       </c>
-      <c r="O21" s="10"/>
-      <c r="P21" s="23" t="s">
+      <c r="O21" s="113"/>
+      <c r="P21" s="114" t="s">
         <v>33</v>
       </c>
-      <c r="Q21" s="24"/>
+      <c r="Q21" s="115"/>
     </row>
     <row r="22" spans="2:23" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="14">
+      <c r="B22" s="11">
         <v>17</v>
       </c>
       <c r="C22" s="3">
@@ -2597,27 +7011,27 @@
       <c r="I22" s="3">
         <v>1</v>
       </c>
-      <c r="J22" s="15">
-        <v>1</v>
-      </c>
-      <c r="M22" s="29" t="s">
+      <c r="J22" s="12">
+        <v>1</v>
+      </c>
+      <c r="M22" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="N22" s="30" t="s">
+      <c r="N22" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="O22" s="50" t="s">
+      <c r="O22" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="P22" s="31" t="s">
+      <c r="P22" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="Q22" s="50" t="s">
+      <c r="Q22" s="41" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B23" s="14">
+      <c r="B23" s="11">
         <v>18</v>
       </c>
       <c r="C23" s="3">
@@ -2641,29 +7055,29 @@
       <c r="I23" s="3">
         <v>1</v>
       </c>
-      <c r="J23" s="15">
-        <v>1</v>
-      </c>
-      <c r="M23" s="25">
-        <v>1</v>
-      </c>
-      <c r="N23" s="26">
+      <c r="J23" s="12">
+        <v>1</v>
+      </c>
+      <c r="M23" s="19">
+        <v>1</v>
+      </c>
+      <c r="N23" s="20">
         <v>44</v>
       </c>
-      <c r="O23" s="27">
+      <c r="O23" s="21">
         <f>360/N23</f>
         <v>8.1818181818181817</v>
       </c>
-      <c r="P23" s="47">
+      <c r="P23" s="38">
         <v>42</v>
       </c>
-      <c r="Q23" s="48">
+      <c r="Q23" s="39">
         <f>360/P23</f>
         <v>8.5714285714285712</v>
       </c>
     </row>
     <row r="24" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B24" s="14">
+      <c r="B24" s="11">
         <v>19</v>
       </c>
       <c r="C24" s="3">
@@ -2687,29 +7101,29 @@
       <c r="I24" s="3">
         <v>1</v>
       </c>
-      <c r="J24" s="15">
-        <v>1</v>
-      </c>
-      <c r="M24" s="20">
+      <c r="J24" s="12">
+        <v>1</v>
+      </c>
+      <c r="M24" s="17">
         <v>2</v>
       </c>
-      <c r="N24" s="18">
+      <c r="N24" s="15">
         <v>45</v>
       </c>
-      <c r="O24" s="27">
+      <c r="O24" s="21">
         <f t="shared" ref="O24:O32" si="3">360/N24</f>
         <v>8</v>
       </c>
-      <c r="P24" s="18">
+      <c r="P24" s="15">
         <v>46</v>
       </c>
-      <c r="Q24" s="27">
+      <c r="Q24" s="21">
         <f t="shared" ref="Q24:Q31" si="4">360/P24</f>
         <v>7.8260869565217392</v>
       </c>
     </row>
     <row r="25" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B25" s="14">
+      <c r="B25" s="11">
         <v>20</v>
       </c>
       <c r="C25" s="3">
@@ -2733,29 +7147,29 @@
       <c r="I25" s="3">
         <v>1</v>
       </c>
-      <c r="J25" s="15">
-        <v>1</v>
-      </c>
-      <c r="M25" s="20">
+      <c r="J25" s="12">
+        <v>1</v>
+      </c>
+      <c r="M25" s="17">
         <v>3</v>
       </c>
-      <c r="N25" s="18">
+      <c r="N25" s="15">
         <v>46</v>
       </c>
-      <c r="O25" s="27">
+      <c r="O25" s="21">
         <f t="shared" si="3"/>
         <v>7.8260869565217392</v>
       </c>
-      <c r="P25" s="18">
+      <c r="P25" s="15">
         <v>45</v>
       </c>
-      <c r="Q25" s="27">
+      <c r="Q25" s="21">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B26" s="14">
+      <c r="B26" s="11">
         <v>21</v>
       </c>
       <c r="C26" s="3">
@@ -2779,29 +7193,29 @@
       <c r="I26" s="3">
         <v>1</v>
       </c>
-      <c r="J26" s="15">
-        <v>1</v>
-      </c>
-      <c r="M26" s="20">
+      <c r="J26" s="12">
+        <v>1</v>
+      </c>
+      <c r="M26" s="17">
         <v>4</v>
       </c>
-      <c r="N26" s="18">
+      <c r="N26" s="15">
         <v>46</v>
       </c>
-      <c r="O26" s="27">
+      <c r="O26" s="21">
         <f t="shared" si="3"/>
         <v>7.8260869565217392</v>
       </c>
-      <c r="P26" s="18">
+      <c r="P26" s="15">
         <v>46</v>
       </c>
-      <c r="Q26" s="27">
+      <c r="Q26" s="21">
         <f t="shared" si="4"/>
         <v>7.8260869565217392</v>
       </c>
     </row>
     <row r="27" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B27" s="14">
+      <c r="B27" s="11">
         <v>22</v>
       </c>
       <c r="C27" s="3">
@@ -2825,29 +7239,29 @@
       <c r="I27" s="3">
         <v>1</v>
       </c>
-      <c r="J27" s="15">
-        <v>1</v>
-      </c>
-      <c r="M27" s="20">
+      <c r="J27" s="12">
+        <v>1</v>
+      </c>
+      <c r="M27" s="17">
         <v>5</v>
       </c>
-      <c r="N27" s="18">
+      <c r="N27" s="15">
         <v>44</v>
       </c>
-      <c r="O27" s="27">
+      <c r="O27" s="21">
         <f t="shared" si="3"/>
         <v>8.1818181818181817</v>
       </c>
-      <c r="P27" s="18">
+      <c r="P27" s="15">
         <v>45</v>
       </c>
-      <c r="Q27" s="27">
+      <c r="Q27" s="21">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
     </row>
     <row r="28" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B28" s="14">
+      <c r="B28" s="11">
         <v>23</v>
       </c>
       <c r="C28" s="3">
@@ -2871,29 +7285,29 @@
       <c r="I28" s="3">
         <v>1</v>
       </c>
-      <c r="J28" s="15">
-        <v>1</v>
-      </c>
-      <c r="M28" s="20">
+      <c r="J28" s="12">
+        <v>1</v>
+      </c>
+      <c r="M28" s="17">
         <v>6</v>
       </c>
-      <c r="N28" s="18">
+      <c r="N28" s="15">
         <v>46</v>
       </c>
-      <c r="O28" s="27">
+      <c r="O28" s="21">
         <f t="shared" si="3"/>
         <v>7.8260869565217392</v>
       </c>
-      <c r="P28" s="18">
+      <c r="P28" s="15">
         <v>46</v>
       </c>
-      <c r="Q28" s="27">
+      <c r="Q28" s="21">
         <f t="shared" si="4"/>
         <v>7.8260869565217392</v>
       </c>
     </row>
     <row r="29" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B29" s="14">
+      <c r="B29" s="11">
         <v>24</v>
       </c>
       <c r="C29" s="3">
@@ -2917,29 +7331,29 @@
       <c r="I29" s="3">
         <v>1</v>
       </c>
-      <c r="J29" s="15">
-        <v>1</v>
-      </c>
-      <c r="M29" s="20">
+      <c r="J29" s="12">
+        <v>1</v>
+      </c>
+      <c r="M29" s="17">
         <v>7</v>
       </c>
-      <c r="N29" s="18">
+      <c r="N29" s="15">
         <v>47</v>
       </c>
-      <c r="O29" s="27">
+      <c r="O29" s="21">
         <f t="shared" si="3"/>
         <v>7.6595744680851068</v>
       </c>
-      <c r="P29" s="18">
+      <c r="P29" s="15">
         <v>45</v>
       </c>
-      <c r="Q29" s="27">
+      <c r="Q29" s="21">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B30" s="14">
+      <c r="B30" s="11">
         <v>25</v>
       </c>
       <c r="C30" s="3">
@@ -2963,29 +7377,29 @@
       <c r="I30" s="3">
         <v>1</v>
       </c>
-      <c r="J30" s="15">
-        <v>1</v>
-      </c>
-      <c r="M30" s="20">
+      <c r="J30" s="12">
+        <v>1</v>
+      </c>
+      <c r="M30" s="17">
         <v>8</v>
       </c>
-      <c r="N30" s="18">
+      <c r="N30" s="15">
         <v>44</v>
       </c>
-      <c r="O30" s="27">
+      <c r="O30" s="21">
         <f t="shared" si="3"/>
         <v>8.1818181818181817</v>
       </c>
-      <c r="P30" s="18">
+      <c r="P30" s="15">
         <v>46</v>
       </c>
-      <c r="Q30" s="27">
+      <c r="Q30" s="21">
         <f t="shared" si="4"/>
         <v>7.8260869565217392</v>
       </c>
     </row>
     <row r="31" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B31" s="14">
+      <c r="B31" s="11">
         <v>26</v>
       </c>
       <c r="C31" s="3">
@@ -3009,29 +7423,29 @@
       <c r="I31" s="3">
         <v>1</v>
       </c>
-      <c r="J31" s="15">
-        <v>1</v>
-      </c>
-      <c r="M31" s="20">
+      <c r="J31" s="12">
+        <v>1</v>
+      </c>
+      <c r="M31" s="17">
         <v>9</v>
       </c>
-      <c r="N31" s="18">
+      <c r="N31" s="15">
         <v>46</v>
       </c>
-      <c r="O31" s="27">
+      <c r="O31" s="21">
         <f t="shared" si="3"/>
         <v>7.8260869565217392</v>
       </c>
-      <c r="P31" s="18">
+      <c r="P31" s="15">
         <v>45</v>
       </c>
-      <c r="Q31" s="27">
+      <c r="Q31" s="21">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
     </row>
     <row r="32" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="14">
+      <c r="B32" s="11">
         <v>27</v>
       </c>
       <c r="C32" s="3">
@@ -3055,29 +7469,29 @@
       <c r="I32" s="3">
         <v>1</v>
       </c>
-      <c r="J32" s="15">
-        <v>1</v>
-      </c>
-      <c r="M32" s="20">
+      <c r="J32" s="12">
+        <v>1</v>
+      </c>
+      <c r="M32" s="17">
         <v>10</v>
       </c>
-      <c r="N32" s="18">
+      <c r="N32" s="15">
         <v>45</v>
       </c>
-      <c r="O32" s="27">
+      <c r="O32" s="21">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="P32" s="19">
+      <c r="P32" s="16">
         <v>46</v>
       </c>
-      <c r="Q32" s="49">
+      <c r="Q32" s="40">
         <f>360/P32</f>
         <v>7.8260869565217392</v>
       </c>
     </row>
     <row r="33" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="14">
+      <c r="B33" s="11">
         <v>28</v>
       </c>
       <c r="C33" s="3">
@@ -3101,25 +7515,25 @@
       <c r="I33" s="3">
         <v>1</v>
       </c>
-      <c r="J33" s="15">
-        <v>1</v>
-      </c>
-      <c r="M33" s="21" t="s">
+      <c r="J33" s="12">
+        <v>1</v>
+      </c>
+      <c r="M33" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="N33" s="9"/>
-      <c r="O33" s="92">
+      <c r="N33" s="111"/>
+      <c r="O33" s="80">
         <f>SUM(O23:O32)/M32</f>
         <v>7.9509376839626595</v>
       </c>
-      <c r="P33" s="93"/>
-      <c r="Q33" s="94">
+      <c r="P33" s="81"/>
+      <c r="Q33" s="82">
         <f>SUM(Q23:Q32)/M32</f>
         <v>7.970186335403727</v>
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="14">
+      <c r="B34" s="11">
         <v>29</v>
       </c>
       <c r="C34" s="3">
@@ -3143,12 +7557,12 @@
       <c r="I34" s="3">
         <v>1</v>
       </c>
-      <c r="J34" s="15">
+      <c r="J34" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="14">
+      <c r="B35" s="11">
         <v>30</v>
       </c>
       <c r="C35" s="3">
@@ -3172,12 +7586,12 @@
       <c r="I35" s="3">
         <v>1</v>
       </c>
-      <c r="J35" s="15">
+      <c r="J35" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B36" s="14">
+      <c r="B36" s="11">
         <v>31</v>
       </c>
       <c r="C36" s="3">
@@ -3201,12 +7615,12 @@
       <c r="I36" s="3">
         <v>1</v>
       </c>
-      <c r="J36" s="15">
+      <c r="J36" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B37" s="14">
+      <c r="B37" s="11">
         <v>32</v>
       </c>
       <c r="C37" s="3">
@@ -3230,12 +7644,12 @@
       <c r="I37" s="3">
         <v>1</v>
       </c>
-      <c r="J37" s="15">
+      <c r="J37" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="14">
+      <c r="B38" s="11">
         <v>33</v>
       </c>
       <c r="C38" s="3">
@@ -3259,12 +7673,12 @@
       <c r="I38" s="3">
         <v>1</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J38" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B39" s="14">
+      <c r="B39" s="11">
         <v>34</v>
       </c>
       <c r="C39" s="3">
@@ -3288,12 +7702,12 @@
       <c r="I39" s="3">
         <v>1</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B40" s="14">
+      <c r="B40" s="11">
         <v>35</v>
       </c>
       <c r="C40" s="3">
@@ -3317,12 +7731,12 @@
       <c r="I40" s="3">
         <v>1</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="14">
+      <c r="B41" s="11">
         <v>36</v>
       </c>
       <c r="C41" s="3">
@@ -3346,12 +7760,12 @@
       <c r="I41" s="3">
         <v>1</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B42" s="14">
+      <c r="B42" s="11">
         <v>37</v>
       </c>
       <c r="C42" s="3">
@@ -3375,12 +7789,12 @@
       <c r="I42" s="3">
         <v>1</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B43" s="14">
+      <c r="B43" s="11">
         <v>38</v>
       </c>
       <c r="C43" s="3">
@@ -3404,12 +7818,12 @@
       <c r="I43" s="3">
         <v>1</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="14">
+      <c r="B44" s="11">
         <v>39</v>
       </c>
       <c r="C44" s="3">
@@ -3433,12 +7847,12 @@
       <c r="I44" s="3">
         <v>1</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B45" s="14">
+      <c r="B45" s="11">
         <v>40</v>
       </c>
       <c r="C45" s="3">
@@ -3462,12 +7876,12 @@
       <c r="I45" s="3">
         <v>1</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B46" s="14">
+      <c r="B46" s="11">
         <v>41</v>
       </c>
       <c r="C46" s="3">
@@ -3491,12 +7905,12 @@
       <c r="I46" s="3">
         <v>1</v>
       </c>
-      <c r="J46" s="15">
+      <c r="J46" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B47" s="14">
+      <c r="B47" s="11">
         <v>42</v>
       </c>
       <c r="C47" s="3">
@@ -3520,12 +7934,12 @@
       <c r="I47" s="3">
         <v>1</v>
       </c>
-      <c r="J47" s="15">
+      <c r="J47" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B48" s="14">
+      <c r="B48" s="11">
         <v>43</v>
       </c>
       <c r="C48" s="3">
@@ -3549,12 +7963,12 @@
       <c r="I48" s="3">
         <v>1</v>
       </c>
-      <c r="J48" s="15">
+      <c r="J48" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B49" s="14">
+      <c r="B49" s="11">
         <v>44</v>
       </c>
       <c r="C49" s="3">
@@ -3578,12 +7992,12 @@
       <c r="I49" s="3">
         <v>1</v>
       </c>
-      <c r="J49" s="15">
+      <c r="J49" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="14">
+      <c r="B50" s="11">
         <v>45</v>
       </c>
       <c r="C50" s="3">
@@ -3607,12 +8021,12 @@
       <c r="I50" s="3">
         <v>1</v>
       </c>
-      <c r="J50" s="15">
+      <c r="J50" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="14">
+      <c r="B51" s="11">
         <v>46</v>
       </c>
       <c r="C51" s="3">
@@ -3636,12 +8050,12 @@
       <c r="I51" s="3">
         <v>1</v>
       </c>
-      <c r="J51" s="15">
+      <c r="J51" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B52" s="14">
+      <c r="B52" s="11">
         <v>47</v>
       </c>
       <c r="C52" s="3">
@@ -3665,12 +8079,12 @@
       <c r="I52" s="3">
         <v>1</v>
       </c>
-      <c r="J52" s="15">
+      <c r="J52" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53" s="14">
+      <c r="B53" s="11">
         <v>48</v>
       </c>
       <c r="C53" s="3">
@@ -3694,12 +8108,12 @@
       <c r="I53" s="3">
         <v>1</v>
       </c>
-      <c r="J53" s="15">
+      <c r="J53" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="14">
+      <c r="B54" s="11">
         <v>49</v>
       </c>
       <c r="C54" s="3">
@@ -3723,12 +8137,12 @@
       <c r="I54" s="3">
         <v>1</v>
       </c>
-      <c r="J54" s="15">
+      <c r="J54" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B55" s="14">
+      <c r="B55" s="11">
         <v>50</v>
       </c>
       <c r="C55" s="3">
@@ -3752,12 +8166,12 @@
       <c r="I55" s="3">
         <v>1</v>
       </c>
-      <c r="J55" s="15">
+      <c r="J55" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B56" s="14">
+      <c r="B56" s="11">
         <v>51</v>
       </c>
       <c r="C56" s="3">
@@ -3781,12 +8195,12 @@
       <c r="I56" s="3">
         <v>1</v>
       </c>
-      <c r="J56" s="15">
+      <c r="J56" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="14">
+      <c r="B57" s="11">
         <v>52</v>
       </c>
       <c r="C57" s="3">
@@ -3810,12 +8224,12 @@
       <c r="I57" s="3">
         <v>1</v>
       </c>
-      <c r="J57" s="15">
+      <c r="J57" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58" s="14">
+      <c r="B58" s="11">
         <v>53</v>
       </c>
       <c r="C58" s="3">
@@ -3839,12 +8253,12 @@
       <c r="I58" s="3">
         <v>1</v>
       </c>
-      <c r="J58" s="15">
+      <c r="J58" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B59" s="14">
+      <c r="B59" s="11">
         <v>54</v>
       </c>
       <c r="C59" s="3">
@@ -3868,12 +8282,12 @@
       <c r="I59" s="3">
         <v>1</v>
       </c>
-      <c r="J59" s="15">
+      <c r="J59" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60" s="14">
+      <c r="B60" s="11">
         <v>55</v>
       </c>
       <c r="C60" s="3">
@@ -3897,12 +8311,12 @@
       <c r="I60" s="3">
         <v>1</v>
       </c>
-      <c r="J60" s="15">
+      <c r="J60" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B61" s="14">
+      <c r="B61" s="11">
         <v>56</v>
       </c>
       <c r="C61" s="3">
@@ -3926,12 +8340,12 @@
       <c r="I61" s="3">
         <v>1</v>
       </c>
-      <c r="J61" s="15">
+      <c r="J61" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B62" s="14">
+      <c r="B62" s="11">
         <v>57</v>
       </c>
       <c r="C62" s="3">
@@ -3955,12 +8369,12 @@
       <c r="I62" s="3">
         <v>1</v>
       </c>
-      <c r="J62" s="15">
+      <c r="J62" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B63" s="14">
+      <c r="B63" s="11">
         <v>58</v>
       </c>
       <c r="C63" s="3">
@@ -3984,12 +8398,12 @@
       <c r="I63" s="3">
         <v>1</v>
       </c>
-      <c r="J63" s="15">
+      <c r="J63" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="14">
+      <c r="B64" s="11">
         <v>59</v>
       </c>
       <c r="C64" s="3">
@@ -4013,12 +8427,12 @@
       <c r="I64" s="3">
         <v>1</v>
       </c>
-      <c r="J64" s="15">
+      <c r="J64" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B65" s="14">
+      <c r="B65" s="11">
         <v>60</v>
       </c>
       <c r="C65" s="3">
@@ -4042,12 +8456,12 @@
       <c r="I65" s="3">
         <v>1</v>
       </c>
-      <c r="J65" s="15">
+      <c r="J65" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B66" s="14">
+      <c r="B66" s="11">
         <v>61</v>
       </c>
       <c r="C66" s="3">
@@ -4071,12 +8485,12 @@
       <c r="I66" s="3">
         <v>1</v>
       </c>
-      <c r="J66" s="15">
+      <c r="J66" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B67" s="14">
+      <c r="B67" s="11">
         <v>62</v>
       </c>
       <c r="C67" s="3">
@@ -4100,12 +8514,12 @@
       <c r="I67" s="3">
         <v>1</v>
       </c>
-      <c r="J67" s="15">
+      <c r="J67" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B68" s="14">
+      <c r="B68" s="11">
         <v>63</v>
       </c>
       <c r="C68" s="3">
@@ -4129,12 +8543,12 @@
       <c r="I68" s="3">
         <v>1</v>
       </c>
-      <c r="J68" s="15">
+      <c r="J68" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B69" s="14">
+      <c r="B69" s="11">
         <v>64</v>
       </c>
       <c r="C69" s="3">
@@ -4158,12 +8572,12 @@
       <c r="I69" s="3">
         <v>1</v>
       </c>
-      <c r="J69" s="15">
+      <c r="J69" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B70" s="14">
+      <c r="B70" s="11">
         <v>65</v>
       </c>
       <c r="C70" s="3">
@@ -4187,12 +8601,12 @@
       <c r="I70" s="3">
         <v>1</v>
       </c>
-      <c r="J70" s="15">
+      <c r="J70" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B71" s="14">
+      <c r="B71" s="11">
         <v>66</v>
       </c>
       <c r="C71" s="3">
@@ -4216,12 +8630,12 @@
       <c r="I71" s="3">
         <v>1</v>
       </c>
-      <c r="J71" s="15">
+      <c r="J71" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B72" s="14">
+      <c r="B72" s="11">
         <v>67</v>
       </c>
       <c r="C72" s="3">
@@ -4245,12 +8659,12 @@
       <c r="I72" s="3">
         <v>1</v>
       </c>
-      <c r="J72" s="15">
+      <c r="J72" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B73" s="14">
+      <c r="B73" s="11">
         <v>68</v>
       </c>
       <c r="C73" s="3">
@@ -4274,12 +8688,12 @@
       <c r="I73" s="3">
         <v>1</v>
       </c>
-      <c r="J73" s="15">
+      <c r="J73" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B74" s="14">
+      <c r="B74" s="11">
         <v>69</v>
       </c>
       <c r="C74" s="3">
@@ -4303,12 +8717,12 @@
       <c r="I74" s="3">
         <v>1</v>
       </c>
-      <c r="J74" s="15">
+      <c r="J74" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B75" s="14">
+      <c r="B75" s="11">
         <v>70</v>
       </c>
       <c r="C75" s="3">
@@ -4332,12 +8746,12 @@
       <c r="I75" s="3">
         <v>1</v>
       </c>
-      <c r="J75" s="15">
+      <c r="J75" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B76" s="14">
+      <c r="B76" s="11">
         <v>71</v>
       </c>
       <c r="C76" s="3">
@@ -4361,12 +8775,12 @@
       <c r="I76" s="3">
         <v>1</v>
       </c>
-      <c r="J76" s="15">
+      <c r="J76" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B77" s="14">
+      <c r="B77" s="11">
         <v>72</v>
       </c>
       <c r="C77" s="3">
@@ -4390,12 +8804,12 @@
       <c r="I77" s="3">
         <v>1</v>
       </c>
-      <c r="J77" s="15">
+      <c r="J77" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B78" s="14">
+      <c r="B78" s="11">
         <v>73</v>
       </c>
       <c r="C78" s="3">
@@ -4419,12 +8833,12 @@
       <c r="I78" s="3">
         <v>1</v>
       </c>
-      <c r="J78" s="15">
+      <c r="J78" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B79" s="14">
+      <c r="B79" s="11">
         <v>74</v>
       </c>
       <c r="C79" s="3">
@@ -4448,12 +8862,12 @@
       <c r="I79" s="3">
         <v>1</v>
       </c>
-      <c r="J79" s="15">
+      <c r="J79" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B80" s="14">
+      <c r="B80" s="11">
         <v>75</v>
       </c>
       <c r="C80" s="3">
@@ -4477,12 +8891,12 @@
       <c r="I80" s="3">
         <v>1</v>
       </c>
-      <c r="J80" s="15">
+      <c r="J80" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B81" s="14">
+      <c r="B81" s="11">
         <v>76</v>
       </c>
       <c r="C81" s="3">
@@ -4506,12 +8920,12 @@
       <c r="I81" s="3">
         <v>1</v>
       </c>
-      <c r="J81" s="15">
+      <c r="J81" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B82" s="14">
+      <c r="B82" s="11">
         <v>77</v>
       </c>
       <c r="C82" s="3">
@@ -4535,12 +8949,12 @@
       <c r="I82" s="3">
         <v>1</v>
       </c>
-      <c r="J82" s="15">
+      <c r="J82" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B83" s="14">
+      <c r="B83" s="11">
         <v>78</v>
       </c>
       <c r="C83" s="3">
@@ -4564,12 +8978,12 @@
       <c r="I83" s="3">
         <v>1</v>
       </c>
-      <c r="J83" s="15">
+      <c r="J83" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B84" s="14">
+      <c r="B84" s="11">
         <v>79</v>
       </c>
       <c r="C84" s="3">
@@ -4593,12 +9007,12 @@
       <c r="I84" s="3">
         <v>1</v>
       </c>
-      <c r="J84" s="15">
+      <c r="J84" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B85" s="14">
+      <c r="B85" s="11">
         <v>80</v>
       </c>
       <c r="C85" s="3">
@@ -4622,12 +9036,12 @@
       <c r="I85" s="3">
         <v>1</v>
       </c>
-      <c r="J85" s="15">
+      <c r="J85" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B86" s="14">
+      <c r="B86" s="11">
         <v>81</v>
       </c>
       <c r="C86" s="3">
@@ -4651,12 +9065,12 @@
       <c r="I86" s="3">
         <v>1</v>
       </c>
-      <c r="J86" s="15">
+      <c r="J86" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B87" s="14">
+      <c r="B87" s="11">
         <v>82</v>
       </c>
       <c r="C87" s="3">
@@ -4680,12 +9094,12 @@
       <c r="I87" s="3">
         <v>1</v>
       </c>
-      <c r="J87" s="15">
+      <c r="J87" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B88" s="14">
+      <c r="B88" s="11">
         <v>83</v>
       </c>
       <c r="C88" s="3">
@@ -4709,12 +9123,12 @@
       <c r="I88" s="3">
         <v>1</v>
       </c>
-      <c r="J88" s="15">
+      <c r="J88" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B89" s="14">
+      <c r="B89" s="11">
         <v>84</v>
       </c>
       <c r="C89" s="3">
@@ -4738,12 +9152,12 @@
       <c r="I89" s="3">
         <v>1</v>
       </c>
-      <c r="J89" s="15">
+      <c r="J89" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B90" s="14">
+      <c r="B90" s="11">
         <v>85</v>
       </c>
       <c r="C90" s="3">
@@ -4767,12 +9181,12 @@
       <c r="I90" s="3">
         <v>1</v>
       </c>
-      <c r="J90" s="15">
+      <c r="J90" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B91" s="14">
+      <c r="B91" s="11">
         <v>86</v>
       </c>
       <c r="C91" s="3">
@@ -4796,12 +9210,12 @@
       <c r="I91" s="3">
         <v>1</v>
       </c>
-      <c r="J91" s="15">
+      <c r="J91" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B92" s="14">
+      <c r="B92" s="11">
         <v>87</v>
       </c>
       <c r="C92" s="3">
@@ -4825,12 +9239,12 @@
       <c r="I92" s="3">
         <v>1</v>
       </c>
-      <c r="J92" s="15">
+      <c r="J92" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B93" s="14">
+      <c r="B93" s="11">
         <v>88</v>
       </c>
       <c r="C93" s="3">
@@ -4854,12 +9268,12 @@
       <c r="I93" s="3">
         <v>1</v>
       </c>
-      <c r="J93" s="15">
+      <c r="J93" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B94" s="14">
+      <c r="B94" s="11">
         <v>89</v>
       </c>
       <c r="C94" s="3">
@@ -4883,12 +9297,12 @@
       <c r="I94" s="3">
         <v>1</v>
       </c>
-      <c r="J94" s="15">
+      <c r="J94" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B95" s="14">
+      <c r="B95" s="11">
         <v>90</v>
       </c>
       <c r="C95" s="3">
@@ -4912,12 +9326,12 @@
       <c r="I95" s="3">
         <v>1</v>
       </c>
-      <c r="J95" s="15">
+      <c r="J95" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B96" s="14">
+      <c r="B96" s="11">
         <v>91</v>
       </c>
       <c r="C96" s="3">
@@ -4941,12 +9355,12 @@
       <c r="I96" s="3">
         <v>1</v>
       </c>
-      <c r="J96" s="15">
+      <c r="J96" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B97" s="14">
+      <c r="B97" s="11">
         <v>92</v>
       </c>
       <c r="C97" s="3">
@@ -4970,12 +9384,12 @@
       <c r="I97" s="3">
         <v>1</v>
       </c>
-      <c r="J97" s="15">
+      <c r="J97" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B98" s="14">
+      <c r="B98" s="11">
         <v>93</v>
       </c>
       <c r="C98" s="3">
@@ -4999,12 +9413,12 @@
       <c r="I98" s="3">
         <v>1</v>
       </c>
-      <c r="J98" s="15">
+      <c r="J98" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B99" s="14">
+      <c r="B99" s="11">
         <v>94</v>
       </c>
       <c r="C99" s="3">
@@ -5028,12 +9442,12 @@
       <c r="I99" s="3">
         <v>0</v>
       </c>
-      <c r="J99" s="15">
+      <c r="J99" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B100" s="14">
+      <c r="B100" s="11">
         <v>95</v>
       </c>
       <c r="C100" s="3">
@@ -5057,12 +9471,12 @@
       <c r="I100" s="3">
         <v>1</v>
       </c>
-      <c r="J100" s="15">
+      <c r="J100" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B101" s="14">
+      <c r="B101" s="11">
         <v>96</v>
       </c>
       <c r="C101" s="3">
@@ -5086,12 +9500,12 @@
       <c r="I101" s="3">
         <v>1</v>
       </c>
-      <c r="J101" s="15">
+      <c r="J101" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B102" s="14">
+      <c r="B102" s="11">
         <v>97</v>
       </c>
       <c r="C102" s="3">
@@ -5115,12 +9529,12 @@
       <c r="I102" s="3">
         <v>1</v>
       </c>
-      <c r="J102" s="15">
+      <c r="J102" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B103" s="14">
+      <c r="B103" s="11">
         <v>98</v>
       </c>
       <c r="C103" s="3">
@@ -5144,12 +9558,12 @@
       <c r="I103" s="3">
         <v>1</v>
       </c>
-      <c r="J103" s="15">
+      <c r="J103" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B104" s="14">
+      <c r="B104" s="11">
         <v>99</v>
       </c>
       <c r="C104" s="3">
@@ -5173,12 +9587,12 @@
       <c r="I104" s="3">
         <v>1</v>
       </c>
-      <c r="J104" s="15">
+      <c r="J104" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="16">
+      <c r="B105" s="13">
         <v>100</v>
       </c>
       <c r="C105" s="3">
@@ -5202,7 +9616,7 @@
       <c r="I105" s="3">
         <v>1</v>
       </c>
-      <c r="J105" s="15">
+      <c r="J105" s="12">
         <v>1</v>
       </c>
     </row>
@@ -5244,7 +9658,7 @@
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" s="51" t="s">
+      <c r="A111" s="42" t="s">
         <v>25</v>
       </c>
       <c r="B111" t="s">
@@ -5743,17 +10157,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="M16:N16"/>
     <mergeCell ref="Y10:AB10"/>
     <mergeCell ref="M20:Q20"/>
     <mergeCell ref="N21:O21"/>
     <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="T10:W10"/>
     <mergeCell ref="M33:N33"/>
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="M3:Q3"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="T10:W10"/>
+    <mergeCell ref="M16:N16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5779,49 +10193,49 @@
   <sheetData>
     <row r="2" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G3" s="63" t="s">
+      <c r="G3" s="119" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="65"/>
+      <c r="H3" s="120"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="121"/>
     </row>
     <row r="4" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G4" s="85" t="s">
+      <c r="G4" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="86" t="s">
+      <c r="H4" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="86" t="s">
+      <c r="I4" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="87" t="s">
+      <c r="J4" s="75" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F5" s="88">
-        <v>1</v>
-      </c>
-      <c r="G5" s="81">
+      <c r="F5" s="76">
+        <v>1</v>
+      </c>
+      <c r="G5" s="69">
         <v>59</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="9">
         <v>59</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="9">
         <v>59</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="10">
         <v>59</v>
       </c>
     </row>
     <row r="6" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F6" s="89">
+      <c r="F6" s="77">
         <v>2</v>
       </c>
-      <c r="G6" s="82">
+      <c r="G6" s="70">
         <v>59</v>
       </c>
       <c r="H6" s="2">
@@ -5830,15 +10244,15 @@
       <c r="I6" s="2">
         <v>56</v>
       </c>
-      <c r="J6" s="72">
+      <c r="J6" s="60">
         <v>66</v>
       </c>
     </row>
     <row r="7" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F7" s="89">
+      <c r="F7" s="77">
         <v>3</v>
       </c>
-      <c r="G7" s="82">
+      <c r="G7" s="70">
         <v>60</v>
       </c>
       <c r="H7" s="2">
@@ -5847,15 +10261,15 @@
       <c r="I7" s="2">
         <v>55</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="60">
         <v>67</v>
       </c>
     </row>
     <row r="8" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F8" s="89">
+      <c r="F8" s="77">
         <v>4</v>
       </c>
-      <c r="G8" s="82">
+      <c r="G8" s="70">
         <v>61</v>
       </c>
       <c r="H8" s="2">
@@ -5864,15 +10278,15 @@
       <c r="I8" s="2">
         <v>55</v>
       </c>
-      <c r="J8" s="72">
+      <c r="J8" s="60">
         <v>67</v>
       </c>
     </row>
     <row r="9" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F9" s="89">
+      <c r="F9" s="77">
         <v>5</v>
       </c>
-      <c r="G9" s="82">
+      <c r="G9" s="70">
         <v>58</v>
       </c>
       <c r="H9" s="2">
@@ -5881,15 +10295,15 @@
       <c r="I9" s="2">
         <v>55</v>
       </c>
-      <c r="J9" s="72">
+      <c r="J9" s="60">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F10" s="89">
+      <c r="F10" s="77">
         <v>6</v>
       </c>
-      <c r="G10" s="82">
+      <c r="G10" s="70">
         <v>59</v>
       </c>
       <c r="H10" s="2">
@@ -5898,15 +10312,15 @@
       <c r="I10" s="2">
         <v>55</v>
       </c>
-      <c r="J10" s="72">
+      <c r="J10" s="60">
         <v>67</v>
       </c>
     </row>
     <row r="11" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F11" s="89">
+      <c r="F11" s="77">
         <v>7</v>
       </c>
-      <c r="G11" s="82">
+      <c r="G11" s="70">
         <v>61</v>
       </c>
       <c r="H11" s="2">
@@ -5915,15 +10329,15 @@
       <c r="I11" s="2">
         <v>52</v>
       </c>
-      <c r="J11" s="72">
+      <c r="J11" s="60">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F12" s="89">
+      <c r="F12" s="77">
         <v>8</v>
       </c>
-      <c r="G12" s="82">
+      <c r="G12" s="70">
         <v>58</v>
       </c>
       <c r="H12" s="2">
@@ -5932,15 +10346,15 @@
       <c r="I12" s="2">
         <v>52</v>
       </c>
-      <c r="J12" s="72">
+      <c r="J12" s="60">
         <v>73</v>
       </c>
     </row>
     <row r="13" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F13" s="89">
+      <c r="F13" s="77">
         <v>9</v>
       </c>
-      <c r="G13" s="82">
+      <c r="G13" s="70">
         <v>61</v>
       </c>
       <c r="H13" s="2">
@@ -5949,15 +10363,15 @@
       <c r="I13" s="2">
         <v>30</v>
       </c>
-      <c r="J13" s="72">
+      <c r="J13" s="60">
         <v>351</v>
       </c>
     </row>
     <row r="14" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="F14" s="89">
+      <c r="F14" s="77">
         <v>10</v>
       </c>
-      <c r="G14" s="82">
+      <c r="G14" s="70">
         <v>59</v>
       </c>
       <c r="H14" s="2">
@@ -5966,149 +10380,149 @@
       <c r="I14" s="2">
         <v>30</v>
       </c>
-      <c r="J14" s="72">
+      <c r="J14" s="60">
         <v>351</v>
       </c>
     </row>
     <row r="15" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F15" s="90">
+      <c r="F15" s="78">
         <v>11</v>
       </c>
-      <c r="G15" s="83">
+      <c r="G15" s="71">
         <v>60</v>
       </c>
-      <c r="H15" s="45">
+      <c r="H15" s="36">
         <v>60</v>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="36">
         <v>30</v>
       </c>
-      <c r="J15" s="84">
+      <c r="J15" s="72">
         <v>351</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="41"/>
-      <c r="B21" s="63" t="s">
+      <c r="A21" s="32"/>
+      <c r="B21" s="119" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="65"/>
+      <c r="C21" s="120"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="120"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="120"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="120"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="120"/>
+      <c r="L21" s="120"/>
+      <c r="M21" s="121"/>
     </row>
     <row r="22" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="66"/>
-      <c r="B22" s="74" t="s">
+      <c r="A22" s="54"/>
+      <c r="B22" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="75" t="s">
+      <c r="C22" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="75" t="s">
+      <c r="D22" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="75" t="s">
+      <c r="E22" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="75" t="s">
+      <c r="F22" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="75" t="s">
+      <c r="G22" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="H22" s="75" t="s">
+      <c r="H22" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="75" t="s">
+      <c r="I22" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="J22" s="76" t="s">
+      <c r="J22" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="K22" s="76" t="s">
+      <c r="K22" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="L22" s="76" t="s">
+      <c r="L22" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="M22" s="77" t="s">
+      <c r="M22" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="Q22" s="63" t="s">
+      <c r="Q22" s="119" t="s">
         <v>35</v>
       </c>
-      <c r="R22" s="64"/>
-      <c r="S22" s="64"/>
-      <c r="T22" s="64"/>
-      <c r="U22" s="65"/>
+      <c r="R22" s="120"/>
+      <c r="S22" s="120"/>
+      <c r="T22" s="120"/>
+      <c r="U22" s="121"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="67">
-        <v>1</v>
-      </c>
-      <c r="B23" s="12">
-        <v>16</v>
-      </c>
-      <c r="C23" s="12">
-        <v>16</v>
-      </c>
-      <c r="D23" s="12">
+      <c r="A23" s="55">
+        <v>1</v>
+      </c>
+      <c r="B23" s="9">
+        <v>16</v>
+      </c>
+      <c r="C23" s="9">
+        <v>16</v>
+      </c>
+      <c r="D23" s="9">
         <v>17</v>
       </c>
-      <c r="E23" s="12">
-        <v>16</v>
-      </c>
-      <c r="F23" s="12">
-        <v>16</v>
-      </c>
-      <c r="G23" s="12">
-        <v>16</v>
-      </c>
-      <c r="H23" s="12">
+      <c r="E23" s="9">
+        <v>16</v>
+      </c>
+      <c r="F23" s="9">
+        <v>16</v>
+      </c>
+      <c r="G23" s="9">
+        <v>16</v>
+      </c>
+      <c r="H23" s="9">
         <v>17</v>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="9">
         <v>19</v>
       </c>
-      <c r="J23" s="12">
-        <v>16</v>
-      </c>
-      <c r="K23" s="12">
+      <c r="J23" s="9">
+        <v>16</v>
+      </c>
+      <c r="K23" s="9">
         <v>17</v>
       </c>
-      <c r="L23" s="12">
-        <v>16</v>
-      </c>
-      <c r="M23" s="13">
+      <c r="L23" s="9">
+        <v>16</v>
+      </c>
+      <c r="M23" s="10">
         <v>17</v>
       </c>
-      <c r="Q23" s="78" t="s">
+      <c r="Q23" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="R23" s="79" t="s">
+      <c r="R23" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="S23" s="79" t="s">
+      <c r="S23" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="T23" s="79" t="s">
+      <c r="T23" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="U23" s="80" t="s">
+      <c r="U23" s="68" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="68">
+      <c r="A24" s="56">
         <v>2</v>
       </c>
       <c r="B24" s="2">
@@ -6144,31 +10558,31 @@
       <c r="L24" s="2">
         <v>16</v>
       </c>
-      <c r="M24" s="72">
+      <c r="M24" s="60">
         <v>15</v>
       </c>
-      <c r="Q24" s="19" t="s">
+      <c r="Q24" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="R24" s="17">
+      <c r="R24" s="14">
         <f>SUM(B43:G43)/6</f>
         <v>16.05</v>
       </c>
-      <c r="S24" s="17">
+      <c r="S24" s="14">
         <f>SUM(J43:M43)/4</f>
         <v>15.950000000000001</v>
       </c>
-      <c r="T24" s="17">
+      <c r="T24" s="14">
         <f>SUM(H43:I43)/2</f>
         <v>16.125</v>
       </c>
-      <c r="U24" s="91">
+      <c r="U24" s="79">
         <f>SUM(R24:T24)/3</f>
         <v>16.041666666666668</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="68">
+      <c r="A25" s="56">
         <v>3</v>
       </c>
       <c r="B25" s="2">
@@ -6204,12 +10618,12 @@
       <c r="L25" s="2">
         <v>16</v>
       </c>
-      <c r="M25" s="72">
+      <c r="M25" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" s="68">
+      <c r="A26" s="56">
         <v>4</v>
       </c>
       <c r="B26" s="2">
@@ -6245,12 +10659,12 @@
       <c r="L26" s="2">
         <v>16</v>
       </c>
-      <c r="M26" s="72">
+      <c r="M26" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="68">
+      <c r="A27" s="56">
         <v>5</v>
       </c>
       <c r="B27" s="2">
@@ -6286,12 +10700,12 @@
       <c r="L27" s="2">
         <v>16</v>
       </c>
-      <c r="M27" s="72">
+      <c r="M27" s="60">
         <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="68">
+      <c r="A28" s="56">
         <v>6</v>
       </c>
       <c r="B28" s="2">
@@ -6327,12 +10741,12 @@
       <c r="L28" s="2">
         <v>16</v>
       </c>
-      <c r="M28" s="72">
+      <c r="M28" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="68">
+      <c r="A29" s="56">
         <v>7</v>
       </c>
       <c r="B29" s="2">
@@ -6368,12 +10782,12 @@
       <c r="L29" s="2">
         <v>16</v>
       </c>
-      <c r="M29" s="72">
+      <c r="M29" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" s="68">
+      <c r="A30" s="56">
         <v>8</v>
       </c>
       <c r="B30" s="2">
@@ -6409,12 +10823,12 @@
       <c r="L30" s="2">
         <v>16</v>
       </c>
-      <c r="M30" s="72">
+      <c r="M30" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="68">
+      <c r="A31" s="56">
         <v>9</v>
       </c>
       <c r="B31" s="2">
@@ -6450,12 +10864,12 @@
       <c r="L31" s="2">
         <v>16</v>
       </c>
-      <c r="M31" s="72">
+      <c r="M31" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A32" s="68">
+      <c r="A32" s="56">
         <v>10</v>
       </c>
       <c r="B32" s="2">
@@ -6491,12 +10905,12 @@
       <c r="L32" s="2">
         <v>16</v>
       </c>
-      <c r="M32" s="72">
+      <c r="M32" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="68">
+      <c r="A33" s="56">
         <v>11</v>
       </c>
       <c r="B33" s="2">
@@ -6532,12 +10946,12 @@
       <c r="L33" s="2">
         <v>16</v>
       </c>
-      <c r="M33" s="72">
+      <c r="M33" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="68">
+      <c r="A34" s="56">
         <v>12</v>
       </c>
       <c r="B34" s="2">
@@ -6573,12 +10987,12 @@
       <c r="L34" s="2">
         <v>16</v>
       </c>
-      <c r="M34" s="72">
+      <c r="M34" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="68">
+      <c r="A35" s="56">
         <v>13</v>
       </c>
       <c r="B35" s="2">
@@ -6614,12 +11028,12 @@
       <c r="L35" s="2">
         <v>16</v>
       </c>
-      <c r="M35" s="72">
+      <c r="M35" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="68">
+      <c r="A36" s="56">
         <v>14</v>
       </c>
       <c r="B36" s="2">
@@ -6655,12 +11069,12 @@
       <c r="L36" s="2">
         <v>15</v>
       </c>
-      <c r="M36" s="72">
+      <c r="M36" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="68">
+      <c r="A37" s="56">
         <v>15</v>
       </c>
       <c r="B37" s="2">
@@ -6696,12 +11110,12 @@
       <c r="L37" s="2">
         <v>17</v>
       </c>
-      <c r="M37" s="72">
+      <c r="M37" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="68">
+      <c r="A38" s="56">
         <v>16</v>
       </c>
       <c r="B38" s="2">
@@ -6737,12 +11151,12 @@
       <c r="L38" s="2">
         <v>16</v>
       </c>
-      <c r="M38" s="72">
+      <c r="M38" s="60">
         <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="68">
+      <c r="A39" s="56">
         <v>17</v>
       </c>
       <c r="B39" s="2">
@@ -6778,12 +11192,12 @@
       <c r="L39" s="2">
         <v>16</v>
       </c>
-      <c r="M39" s="72">
+      <c r="M39" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="68">
+      <c r="A40" s="56">
         <v>18</v>
       </c>
       <c r="B40" s="2">
@@ -6819,12 +11233,12 @@
       <c r="L40" s="2">
         <v>16</v>
       </c>
-      <c r="M40" s="72">
+      <c r="M40" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="68">
+      <c r="A41" s="56">
         <v>19</v>
       </c>
       <c r="B41" s="2">
@@ -6860,12 +11274,12 @@
       <c r="L41" s="2">
         <v>16</v>
       </c>
-      <c r="M41" s="72">
+      <c r="M41" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="69">
+      <c r="A42" s="57">
         <v>20</v>
       </c>
       <c r="B42" s="2">
@@ -6883,7 +11297,7 @@
       <c r="F42" s="2">
         <v>16</v>
       </c>
-      <c r="G42" s="73">
+      <c r="G42" s="61">
         <v>17</v>
       </c>
       <c r="H42" s="2">
@@ -6892,7 +11306,7 @@
       <c r="I42" s="2">
         <v>16</v>
       </c>
-      <c r="J42" s="73">
+      <c r="J42" s="61">
         <v>16</v>
       </c>
       <c r="K42" s="2">
@@ -6901,59 +11315,59 @@
       <c r="L42" s="2">
         <v>16</v>
       </c>
-      <c r="M42" s="72">
+      <c r="M42" s="60">
         <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="70" t="s">
+      <c r="A43" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="B43" s="70">
+      <c r="B43" s="58">
         <f>SUM(B23:B42)/20</f>
         <v>16</v>
       </c>
-      <c r="C43" s="70">
+      <c r="C43" s="58">
         <f t="shared" ref="C43:M43" si="0">SUM(C23:C42)/20</f>
         <v>16.05</v>
       </c>
-      <c r="D43" s="70">
+      <c r="D43" s="58">
         <f t="shared" si="0"/>
         <v>16.149999999999999</v>
       </c>
-      <c r="E43" s="70">
+      <c r="E43" s="58">
         <f t="shared" si="0"/>
         <v>16.05</v>
       </c>
-      <c r="F43" s="70">
+      <c r="F43" s="58">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="G43" s="70">
+      <c r="G43" s="58">
         <f t="shared" si="0"/>
         <v>16.05</v>
       </c>
-      <c r="H43" s="70">
+      <c r="H43" s="58">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="I43" s="70">
+      <c r="I43" s="58">
         <f t="shared" si="0"/>
         <v>16.25</v>
       </c>
-      <c r="J43" s="70">
+      <c r="J43" s="58">
         <f t="shared" si="0"/>
         <v>15.7</v>
       </c>
-      <c r="K43" s="70">
+      <c r="K43" s="58">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="L43" s="70">
+      <c r="L43" s="58">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="M43" s="70">
+      <c r="M43" s="58">
         <f t="shared" si="0"/>
         <v>16.100000000000001</v>
       </c>
@@ -6986,44 +11400,44 @@
     </row>
     <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="98" t="s">
+      <c r="C7" s="122" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="99"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="100"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="124"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="85" t="s">
+      <c r="C8" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="103" t="s">
+      <c r="D8" s="88" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="103" t="s">
+      <c r="E8" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="104" t="s">
+      <c r="F8" s="89" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C9" s="101">
-        <v>1</v>
-      </c>
-      <c r="D9" s="28">
+      <c r="C9" s="86">
+        <v>1</v>
+      </c>
+      <c r="D9" s="22">
         <v>9.9</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="22">
         <v>10</v>
       </c>
-      <c r="F9" s="102">
+      <c r="F9" s="87">
         <f>ABS((D9-E9))/E9</f>
         <v>9.9999999999999638E-3</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C10" s="82">
+      <c r="C10" s="70">
         <v>2</v>
       </c>
       <c r="D10" s="3">
@@ -7032,13 +11446,13 @@
       <c r="E10" s="3">
         <v>20.3</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="83">
         <f>(ABS((D10-E10))/E10)</f>
         <v>1.4778325123152743E-2</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C11" s="82">
+      <c r="C11" s="70">
         <v>3</v>
       </c>
       <c r="D11" s="3">
@@ -7047,13 +11461,13 @@
       <c r="E11" s="3">
         <v>5</v>
       </c>
-      <c r="F11" s="95">
-        <f t="shared" ref="F10:F18" si="0">ABS((D11-E11))/E11</f>
+      <c r="F11" s="83">
+        <f t="shared" ref="F11:F18" si="0">ABS((D11-E11))/E11</f>
         <v>8.0000000000000071E-2</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C12" s="82">
+      <c r="C12" s="70">
         <v>4</v>
       </c>
       <c r="D12" s="3">
@@ -7062,13 +11476,13 @@
       <c r="E12" s="3">
         <v>15</v>
       </c>
-      <c r="F12" s="95">
+      <c r="F12" s="83">
         <f t="shared" si="0"/>
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C13" s="82">
+      <c r="C13" s="70">
         <v>5</v>
       </c>
       <c r="D13" s="3">
@@ -7077,13 +11491,13 @@
       <c r="E13" s="3">
         <v>25.5</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="83">
         <f t="shared" si="0"/>
         <v>1.9607843137254902E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C14" s="82">
+      <c r="C14" s="70">
         <v>6</v>
       </c>
       <c r="D14" s="3">
@@ -7092,13 +11506,13 @@
       <c r="E14" s="3">
         <v>30</v>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="83">
         <f t="shared" si="0"/>
         <v>9.333333333333324E-2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" s="82">
+      <c r="C15" s="70">
         <v>7</v>
       </c>
       <c r="D15" s="3">
@@ -7107,13 +11521,13 @@
       <c r="E15" s="3">
         <v>35</v>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="83">
         <f t="shared" si="0"/>
         <v>5.7142857142857958E-3</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C16" s="82">
+      <c r="C16" s="70">
         <v>8</v>
       </c>
       <c r="D16" s="3">
@@ -7122,13 +11536,13 @@
       <c r="E16" s="3">
         <v>10</v>
       </c>
-      <c r="F16" s="95">
+      <c r="F16" s="83">
         <f t="shared" si="0"/>
         <v>3.0000000000000072E-2</v>
       </c>
     </row>
     <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="82">
+      <c r="C17" s="70">
         <v>9</v>
       </c>
       <c r="D17" s="3">
@@ -7137,32 +11551,32 @@
       <c r="E17" s="3">
         <v>22</v>
       </c>
-      <c r="F17" s="95">
+      <c r="F17" s="83">
         <f t="shared" si="0"/>
         <v>2.2727272727272728E-2</v>
       </c>
     </row>
     <row r="18" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="83">
+      <c r="C18" s="71">
         <v>10</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="14">
         <v>32.5</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="14">
         <v>33</v>
       </c>
-      <c r="F18" s="96">
+      <c r="F18" s="84">
         <f t="shared" si="0"/>
         <v>1.5151515151515152E-2</v>
       </c>
     </row>
     <row r="19" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="1"/>
-      <c r="E19" s="105" t="s">
+      <c r="E19" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="F19" s="106">
+      <c r="F19" s="91">
         <f>SUM(F9:F18)/C18</f>
         <v>3.5797924185348121E-2</v>
       </c>
@@ -7180,44 +11594,44 @@
       <c r="C23" s="1"/>
     </row>
     <row r="24" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="98" t="s">
+      <c r="C24" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="99"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="100"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="124"/>
     </row>
     <row r="25" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="85" t="s">
+      <c r="C25" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="103" t="s">
+      <c r="D25" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="103" t="s">
+      <c r="E25" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="104" t="s">
+      <c r="F25" s="89" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="26" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C26" s="101">
-        <v>1</v>
-      </c>
-      <c r="D26" s="28">
+      <c r="C26" s="86">
+        <v>1</v>
+      </c>
+      <c r="D26" s="22">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="22">
         <v>10</v>
       </c>
-      <c r="F26" s="102">
+      <c r="F26" s="87">
         <f>ABS((D26-E26))/E26</f>
         <v>8.0000000000000071E-2</v>
       </c>
     </row>
     <row r="27" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C27" s="82">
+      <c r="C27" s="70">
         <v>2</v>
       </c>
       <c r="D27" s="3">
@@ -7226,13 +11640,13 @@
       <c r="E27" s="3">
         <v>20</v>
       </c>
-      <c r="F27" s="95">
+      <c r="F27" s="83">
         <f t="shared" ref="F27:F35" si="1">ABS((D27-E27))/E27</f>
         <v>9.0000000000000038E-2</v>
       </c>
     </row>
     <row r="28" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C28" s="82">
+      <c r="C28" s="70">
         <v>3</v>
       </c>
       <c r="D28" s="3">
@@ -7241,13 +11655,13 @@
       <c r="E28" s="3">
         <v>5</v>
       </c>
-      <c r="F28" s="95">
+      <c r="F28" s="83">
         <f t="shared" si="1"/>
         <v>8.0000000000000071E-2</v>
       </c>
     </row>
     <row r="29" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C29" s="82">
+      <c r="C29" s="70">
         <v>4</v>
       </c>
       <c r="D29" s="3">
@@ -7256,13 +11670,13 @@
       <c r="E29" s="3">
         <v>15</v>
       </c>
-      <c r="F29" s="95">
+      <c r="F29" s="83">
         <f t="shared" si="1"/>
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="30" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C30" s="82">
+      <c r="C30" s="70">
         <v>5</v>
       </c>
       <c r="D30" s="3">
@@ -7271,13 +11685,13 @@
       <c r="E30" s="3">
         <v>25</v>
       </c>
-      <c r="F30" s="95">
+      <c r="F30" s="83">
         <f t="shared" si="1"/>
         <v>0.08</v>
       </c>
     </row>
     <row r="31" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C31" s="82">
+      <c r="C31" s="70">
         <v>6</v>
       </c>
       <c r="D31" s="3">
@@ -7286,13 +11700,13 @@
       <c r="E31" s="3">
         <v>30</v>
       </c>
-      <c r="F31" s="95">
+      <c r="F31" s="83">
         <f t="shared" si="1"/>
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="32" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C32" s="82">
+      <c r="C32" s="70">
         <v>7</v>
       </c>
       <c r="D32" s="3">
@@ -7301,13 +11715,13 @@
       <c r="E32" s="3">
         <v>35</v>
       </c>
-      <c r="F32" s="95">
+      <c r="F32" s="83">
         <f t="shared" si="1"/>
         <v>8.5714285714285715E-2</v>
       </c>
     </row>
     <row r="33" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C33" s="82">
+      <c r="C33" s="70">
         <v>8</v>
       </c>
       <c r="D33" s="3">
@@ -7316,13 +11730,13 @@
       <c r="E33" s="3">
         <v>10</v>
       </c>
-      <c r="F33" s="95">
+      <c r="F33" s="83">
         <f t="shared" si="1"/>
         <v>9.0000000000000038E-2</v>
       </c>
     </row>
     <row r="34" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C34" s="82">
+      <c r="C34" s="70">
         <v>9</v>
       </c>
       <c r="D34" s="3">
@@ -7331,32 +11745,32 @@
       <c r="E34" s="3">
         <v>22</v>
       </c>
-      <c r="F34" s="95">
+      <c r="F34" s="83">
         <f t="shared" si="1"/>
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
     <row r="35" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="83">
+      <c r="C35" s="71">
         <v>10</v>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="14">
         <v>33.200000000000003</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="14">
         <v>33</v>
       </c>
-      <c r="F35" s="96">
+      <c r="F35" s="84">
         <f t="shared" si="1"/>
         <v>6.0606060606061465E-3</v>
       </c>
     </row>
     <row r="36" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C36" s="1"/>
-      <c r="E36" s="105" t="s">
+      <c r="E36" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="F36" s="106">
+      <c r="F36" s="91">
         <f>SUM(F26:F35)/C35</f>
         <v>6.9056277056277079E-2</v>
       </c>
@@ -7383,638 +11797,1000 @@
   <sheetData>
     <row r="2" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="86" t="s">
+      <c r="C3" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="87" t="s">
+      <c r="E3" s="75" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="108">
-        <v>1</v>
-      </c>
-      <c r="D4" s="108">
+      <c r="C4" s="93">
+        <v>1</v>
+      </c>
+      <c r="D4" s="93">
         <v>220</v>
       </c>
-      <c r="E4" s="109">
+      <c r="E4" s="94">
         <v>220</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="97" t="s">
+      <c r="B5" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="110">
-        <v>1</v>
-      </c>
-      <c r="D5" s="110">
+      <c r="C5" s="95">
+        <v>1</v>
+      </c>
+      <c r="D5" s="95">
         <v>52</v>
       </c>
-      <c r="E5" s="111">
+      <c r="E5" s="96">
         <v>52</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="97" t="s">
+      <c r="B6" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="110">
+      <c r="C6" s="95">
         <v>2</v>
       </c>
-      <c r="D6" s="110">
+      <c r="D6" s="95">
         <v>4</v>
       </c>
-      <c r="E6" s="111">
+      <c r="E6" s="96">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="97" t="s">
+      <c r="B7" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="110">
+      <c r="C7" s="95">
         <v>4</v>
       </c>
-      <c r="D7" s="110">
+      <c r="D7" s="95">
         <v>2</v>
       </c>
-      <c r="E7" s="111">
+      <c r="E7" s="96">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="97" t="s">
+      <c r="B8" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="110">
+      <c r="C8" s="95">
         <v>2</v>
       </c>
-      <c r="D8" s="110">
+      <c r="D8" s="95">
         <v>3</v>
       </c>
-      <c r="E8" s="111">
+      <c r="E8" s="96">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="97" t="s">
+      <c r="B9" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="110">
+      <c r="C9" s="95">
         <v>2</v>
       </c>
-      <c r="D9" s="110">
+      <c r="D9" s="95">
         <v>2</v>
       </c>
-      <c r="E9" s="111">
+      <c r="E9" s="96">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="97" t="s">
+      <c r="B10" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="110">
+      <c r="C10" s="95">
         <v>4</v>
       </c>
-      <c r="D10" s="110">
-        <v>1</v>
-      </c>
-      <c r="E10" s="111">
+      <c r="D10" s="95">
+        <v>1</v>
+      </c>
+      <c r="E10" s="96">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="97" t="s">
+      <c r="B11" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="110">
+      <c r="C11" s="95">
         <v>8</v>
       </c>
-      <c r="D11" s="110">
-        <v>1</v>
-      </c>
-      <c r="E11" s="111">
+      <c r="D11" s="95">
+        <v>1</v>
+      </c>
+      <c r="E11" s="96">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="97" t="s">
+      <c r="B12" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="110">
+      <c r="C12" s="95">
         <v>2</v>
       </c>
-      <c r="D12" s="110">
+      <c r="D12" s="95">
         <v>2</v>
       </c>
-      <c r="E12" s="111">
+      <c r="E12" s="96">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="97" t="s">
+      <c r="B13" s="85" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="110" t="s">
+      <c r="C13" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="110">
+      <c r="D13" s="95">
         <v>5</v>
       </c>
-      <c r="E13" s="111">
+      <c r="E13" s="96">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="110" t="s">
+      <c r="C14" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="110">
+      <c r="D14" s="95">
         <v>10</v>
       </c>
-      <c r="E14" s="111">
+      <c r="E14" s="96">
         <v>20</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="112" t="s">
+      <c r="B15" s="97" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="113">
+      <c r="C15" s="98">
         <v>5</v>
       </c>
-      <c r="D15" s="113">
+      <c r="D15" s="98">
         <v>5</v>
       </c>
-      <c r="E15" s="114">
+      <c r="E15" s="99">
         <v>25</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="115" t="s">
+      <c r="B16" s="100" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="116"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="117" t="s">
+      <c r="C16" s="101"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="102" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
     </row>
     <row r="18" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="85" t="s">
+      <c r="B18" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="86" t="s">
+      <c r="C18" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="86" t="s">
+      <c r="D18" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="87" t="s">
+      <c r="E18" s="75" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="107" t="s">
+      <c r="B19" s="92" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="108">
+      <c r="C19" s="93">
         <v>2</v>
       </c>
-      <c r="D19" s="108">
+      <c r="D19" s="93">
         <v>25</v>
       </c>
-      <c r="E19" s="109">
+      <c r="E19" s="94">
         <v>50</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="97" t="s">
+      <c r="B20" s="85" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="110">
-        <v>1</v>
-      </c>
-      <c r="D20" s="110">
+      <c r="C20" s="95">
+        <v>1</v>
+      </c>
+      <c r="D20" s="95">
         <v>20</v>
       </c>
-      <c r="E20" s="111">
+      <c r="E20" s="96">
         <v>20</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="112" t="s">
+      <c r="B21" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="113">
+      <c r="C21" s="98">
         <v>2</v>
       </c>
-      <c r="D21" s="113">
+      <c r="D21" s="98">
         <v>5</v>
       </c>
-      <c r="E21" s="114">
+      <c r="E21" s="99">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="115" t="s">
+      <c r="B22" s="100" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="117" t="s">
+      <c r="C22" s="101"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="102" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
     </row>
     <row r="24" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="85" t="s">
+      <c r="B24" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="C24" s="118" t="s">
+      <c r="C24" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="118" t="s">
+      <c r="D24" s="103" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="117" t="s">
+      <c r="E24" s="102" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="107" t="s">
+      <c r="B25" s="92" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="108" t="s">
+      <c r="C25" s="93" t="s">
         <v>83</v>
       </c>
-      <c r="D25" s="108">
+      <c r="D25" s="93">
         <v>223</v>
       </c>
-      <c r="E25" s="109">
+      <c r="E25" s="94">
         <v>669</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B26" s="97" t="s">
+      <c r="B26" s="85" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="110" t="s">
+      <c r="C26" s="95" t="s">
         <v>85</v>
       </c>
-      <c r="D26" s="110">
+      <c r="D26" s="95">
         <v>12</v>
       </c>
-      <c r="E26" s="111">
+      <c r="E26" s="96">
         <v>1260</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="97" t="s">
+      <c r="B27" s="85" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="110">
-        <v>1</v>
-      </c>
-      <c r="D27" s="110">
+      <c r="C27" s="95">
+        <v>1</v>
+      </c>
+      <c r="D27" s="95">
         <v>60</v>
       </c>
-      <c r="E27" s="111">
+      <c r="E27" s="96">
         <v>60</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="97" t="s">
+      <c r="B28" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="110">
-        <v>1</v>
-      </c>
-      <c r="D28" s="110">
+      <c r="C28" s="95">
+        <v>1</v>
+      </c>
+      <c r="D28" s="95">
         <v>60</v>
       </c>
-      <c r="E28" s="111">
+      <c r="E28" s="96">
         <v>60</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="97" t="s">
+      <c r="B29" s="85" t="s">
         <v>88</v>
       </c>
-      <c r="C29" s="110" t="s">
+      <c r="C29" s="95" t="s">
         <v>89</v>
       </c>
-      <c r="D29" s="110">
+      <c r="D29" s="95">
         <v>20</v>
       </c>
-      <c r="E29" s="111">
+      <c r="E29" s="96">
         <v>60</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="97" t="s">
+      <c r="B30" s="85" t="s">
         <v>90</v>
       </c>
-      <c r="C30" s="110">
+      <c r="C30" s="95">
         <v>2</v>
       </c>
-      <c r="D30" s="110">
+      <c r="D30" s="95">
         <v>2</v>
       </c>
-      <c r="E30" s="111">
+      <c r="E30" s="96">
         <v>4</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="112" t="s">
+      <c r="B31" s="97" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="113">
-        <v>1</v>
-      </c>
-      <c r="D31" s="113">
+      <c r="C31" s="98">
+        <v>1</v>
+      </c>
+      <c r="D31" s="98">
         <v>45</v>
       </c>
-      <c r="E31" s="114">
+      <c r="E31" s="99">
         <v>45</v>
       </c>
     </row>
     <row r="32" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="115" t="s">
+      <c r="B32" s="100" t="s">
         <v>92</v>
       </c>
-      <c r="C32" s="116"/>
-      <c r="D32" s="116"/>
-      <c r="E32" s="117" t="s">
+      <c r="C32" s="101"/>
+      <c r="D32" s="101"/>
+      <c r="E32" s="102" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
     </row>
     <row r="34" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="53"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
     </row>
     <row r="35" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="85" t="s">
+      <c r="B35" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="118" t="s">
+      <c r="C35" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="D35" s="118" t="s">
+      <c r="D35" s="103" t="s">
         <v>60</v>
       </c>
-      <c r="E35" s="117" t="s">
+      <c r="E35" s="102" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="36" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="119" t="s">
+      <c r="B36" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="C36" s="120">
-        <v>1</v>
-      </c>
-      <c r="D36" s="120">
+      <c r="C36" s="105">
+        <v>1</v>
+      </c>
+      <c r="D36" s="105">
         <v>150</v>
       </c>
-      <c r="E36" s="121">
+      <c r="E36" s="106">
         <v>150</v>
       </c>
     </row>
     <row r="37" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="115" t="s">
+      <c r="B37" s="100" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="116"/>
-      <c r="D37" s="116"/>
-      <c r="E37" s="117" t="s">
+      <c r="C37" s="101"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="102" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="38" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="53"/>
-      <c r="C38" s="53"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="53"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
     </row>
     <row r="39" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="85" t="s">
+      <c r="B39" s="73" t="s">
         <v>98</v>
       </c>
-      <c r="C39" s="118" t="s">
+      <c r="C39" s="103" t="s">
         <v>99</v>
       </c>
-      <c r="D39" s="118" t="s">
+      <c r="D39" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="E39" s="117" t="s">
+      <c r="E39" s="102" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B40" s="107" t="s">
+      <c r="B40" s="92" t="s">
         <v>101</v>
       </c>
-      <c r="C40" s="108" t="s">
+      <c r="C40" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="D40" s="108">
+      <c r="D40" s="93">
         <v>240</v>
       </c>
-      <c r="E40" s="109">
+      <c r="E40" s="94">
         <v>4320</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B41" s="97" t="s">
+      <c r="B41" s="85" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="110" t="s">
+      <c r="C41" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="D41" s="110">
+      <c r="D41" s="95">
         <v>240</v>
       </c>
-      <c r="E41" s="111">
+      <c r="E41" s="96">
         <v>8160</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B42" s="97" t="s">
+      <c r="B42" s="85" t="s">
         <v>105</v>
       </c>
-      <c r="C42" s="110" t="s">
+      <c r="C42" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="110">
+      <c r="D42" s="95">
         <v>240</v>
       </c>
-      <c r="E42" s="111">
+      <c r="E42" s="96">
         <v>2880</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B43" s="97" t="s">
+      <c r="B43" s="85" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="110" t="s">
+      <c r="C43" s="95" t="s">
         <v>108</v>
       </c>
-      <c r="D43" s="110">
+      <c r="D43" s="95">
         <v>240</v>
       </c>
-      <c r="E43" s="111">
+      <c r="E43" s="96">
         <v>10560</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B44" s="97" t="s">
+      <c r="B44" s="85" t="s">
         <v>109</v>
       </c>
-      <c r="C44" s="110" t="s">
+      <c r="C44" s="95" t="s">
         <v>110</v>
       </c>
-      <c r="D44" s="110">
+      <c r="D44" s="95">
         <v>240</v>
       </c>
-      <c r="E44" s="111">
+      <c r="E44" s="96">
         <v>1680</v>
       </c>
     </row>
     <row r="45" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="112" t="s">
+      <c r="B45" s="97" t="s">
         <v>111</v>
       </c>
-      <c r="C45" s="113" t="s">
+      <c r="C45" s="98" t="s">
         <v>112</v>
       </c>
-      <c r="D45" s="113">
+      <c r="D45" s="98">
         <v>20</v>
       </c>
-      <c r="E45" s="114">
+      <c r="E45" s="99">
         <v>80</v>
       </c>
     </row>
     <row r="46" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="115" t="s">
+      <c r="B46" s="100" t="s">
         <v>113</v>
       </c>
-      <c r="C46" s="116"/>
-      <c r="D46" s="116"/>
-      <c r="E46" s="117" t="s">
+      <c r="C46" s="101"/>
+      <c r="D46" s="101"/>
+      <c r="E46" s="102" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="47" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="53"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="53"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="44"/>
     </row>
     <row r="48" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="85" t="s">
+      <c r="B48" s="73" t="s">
         <v>115</v>
       </c>
-      <c r="C48" s="117" t="s">
+      <c r="C48" s="102" t="s">
         <v>116</v>
       </c>
-      <c r="D48" s="53"/>
-      <c r="E48" s="53"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="44"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="122" t="s">
+      <c r="B49" s="107" t="s">
         <v>117</v>
       </c>
-      <c r="C49" s="108">
+      <c r="C49" s="93">
         <v>369</v>
       </c>
-      <c r="D49" s="53"/>
-      <c r="E49" s="53"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="44"/>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C50" s="110">
+      <c r="C50" s="95">
         <v>80</v>
       </c>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C51" s="110">
+      <c r="C51" s="95">
         <v>2158</v>
       </c>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="44"/>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C52" s="110">
+      <c r="C52" s="95">
         <v>150</v>
       </c>
-      <c r="D52" s="53"/>
-      <c r="E52" s="53"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
     </row>
     <row r="53" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="71" t="s">
+      <c r="B53" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="C53" s="113">
+      <c r="C53" s="98">
         <v>27680</v>
       </c>
-      <c r="D53" s="53"/>
-      <c r="E53" s="53"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
     </row>
     <row r="54" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="115" t="s">
+      <c r="B54" s="100" t="s">
         <v>122</v>
       </c>
-      <c r="C54" s="117" t="s">
+      <c r="C54" s="102" t="s">
         <v>123</v>
       </c>
-      <c r="D54" s="53"/>
-      <c r="E54" s="53"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B5:E74"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="108">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="108">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="108">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="108">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="109">
+        <v>0.18107416879795402</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="109">
+        <v>0.17025901942645572</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="109">
+        <v>4.9062316037340459E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="109">
+        <v>2.9813664596272993E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="122" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" s="123"/>
+      <c r="D50" s="123"/>
+      <c r="E50" s="124"/>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="86">
+        <v>1</v>
+      </c>
+      <c r="C51" s="108">
+        <v>9.9999999999999638E-3</v>
+      </c>
+      <c r="D51" s="108">
+        <v>3.5797924185348121E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" s="70">
+        <v>2</v>
+      </c>
+      <c r="C52" s="108">
+        <v>1.4778325123152743E-2</v>
+      </c>
+      <c r="D52" s="108">
+        <v>3.5797924185348121E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" s="70">
+        <v>3</v>
+      </c>
+      <c r="C53" s="108">
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="D53" s="108">
+        <v>3.5797924185348121E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" s="70">
+        <v>4</v>
+      </c>
+      <c r="C54" s="108">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D54" s="108">
+        <v>3.5797924185348121E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="70">
+        <v>5</v>
+      </c>
+      <c r="C55" s="108">
+        <v>1.9607843137254902E-2</v>
+      </c>
+      <c r="D55" s="108">
+        <v>3.5797924185348121E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B56" s="70">
+        <v>6</v>
+      </c>
+      <c r="C56" s="108">
+        <v>9.333333333333324E-2</v>
+      </c>
+      <c r="D56" s="108">
+        <v>3.5797924185348121E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" s="70">
+        <v>7</v>
+      </c>
+      <c r="C57" s="108">
+        <v>5.7142857142857958E-3</v>
+      </c>
+      <c r="D57" s="108">
+        <v>3.5797924185348121E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58" s="70">
+        <v>8</v>
+      </c>
+      <c r="C58" s="108">
+        <v>3.0000000000000072E-2</v>
+      </c>
+      <c r="D58" s="108">
+        <v>3.5797924185348121E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" s="70">
+        <v>9</v>
+      </c>
+      <c r="C59" s="108">
+        <v>2.2727272727272728E-2</v>
+      </c>
+      <c r="D59" s="108">
+        <v>3.5797924185348121E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="71">
+        <v>10</v>
+      </c>
+      <c r="C60" s="108">
+        <v>1.5151515151515152E-2</v>
+      </c>
+      <c r="D60" s="108">
+        <v>3.5797924185348121E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" s="122" t="s">
+        <v>49</v>
+      </c>
+      <c r="C64" s="123"/>
+      <c r="D64" s="123"/>
+      <c r="E64" s="124"/>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B65" s="86">
+        <v>1</v>
+      </c>
+      <c r="C65" s="108">
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="D65" s="108">
+        <v>6.9056277056277079E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B66" s="70">
+        <v>2</v>
+      </c>
+      <c r="C66" s="108">
+        <v>9.0000000000000038E-2</v>
+      </c>
+      <c r="D66" s="108">
+        <v>6.9056277056277079E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B67" s="70">
+        <v>3</v>
+      </c>
+      <c r="C67" s="108">
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="D67" s="108">
+        <v>6.9056277056277079E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B68" s="70">
+        <v>4</v>
+      </c>
+      <c r="C68" s="108">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D68" s="108">
+        <v>6.9056277056277079E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B69" s="70">
+        <v>5</v>
+      </c>
+      <c r="C69" s="108">
+        <v>0.08</v>
+      </c>
+      <c r="D69" s="108">
+        <v>6.9056277056277079E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B70" s="70">
+        <v>6</v>
+      </c>
+      <c r="C70" s="108">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="D70" s="108">
+        <v>6.9056277056277079E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B71" s="70">
+        <v>7</v>
+      </c>
+      <c r="C71" s="108">
+        <v>8.5714285714285715E-2</v>
+      </c>
+      <c r="D71" s="108">
+        <v>6.9056277056277079E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B72" s="70">
+        <v>8</v>
+      </c>
+      <c r="C72" s="108">
+        <v>9.0000000000000038E-2</v>
+      </c>
+      <c r="D72" s="108">
+        <v>6.9056277056277079E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B73" s="70">
+        <v>9</v>
+      </c>
+      <c r="C73" s="108">
+        <v>4.5454545454545456E-2</v>
+      </c>
+      <c r="D73" s="108">
+        <v>6.9056277056277079E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="71">
+        <v>10</v>
+      </c>
+      <c r="C74" s="108">
+        <v>6.0606060606061465E-3</v>
+      </c>
+      <c r="D74" s="108">
+        <v>6.9056277056277079E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B64:E64"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>